--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\An3\sem2\VVSS\Lab\MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958ACBB4-C53D-4AE4-B7DB-5E13C1046FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9037656C-DA08-456D-ABE1-B44D8F2BEB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="650" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="87">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Tool-based Code Analysis</t>
   </si>
   <si>
-    <t>Effort to perform tool-based code analysis (hours):</t>
-  </si>
-  <si>
     <t>Husăsan Smaranda-Ioana</t>
   </si>
   <si>
@@ -207,6 +204,99 @@
   </si>
   <si>
     <t>ReceiptGenerator</t>
+  </si>
+  <si>
+    <t>AbstractRepository, Line 37</t>
+  </si>
+  <si>
+    <t>Nu modificam pentru ca logica codului este corecta. Metoda put a dictionarului face update daca exista deja cheie si save daca nu exista cheia</t>
+  </si>
+  <si>
+    <t>AbstractRepository, Line 8</t>
+  </si>
+  <si>
+    <t>Type parameter names should comply with a naming convention</t>
+  </si>
+  <si>
+    <t>Methods should not have identical implementations</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Redundant casts should not be used</t>
+  </si>
+  <si>
+    <t>AbstractRepository, Line 20</t>
+  </si>
+  <si>
+    <t>return (List&lt;E&gt;)StreamSupport.stream(entities.values().spliterator(), false).toList();</t>
+  </si>
+  <si>
+    <t>return StreamSupport.stream(entities.values().spliterator(), false).toList();</t>
+  </si>
+  <si>
+    <t>AbstractRepoSitory, Line 20</t>
+  </si>
+  <si>
+    <t>Sections of code should not be commented out</t>
+  </si>
+  <si>
+    <t>DailyReportService</t>
+  </si>
+  <si>
+    <t>Unnecessary imports should be removed</t>
+  </si>
+  <si>
+    <t>Removed unused imports</t>
+  </si>
+  <si>
+    <t>Multiple variables should not be declared on the same line</t>
+  </si>
+  <si>
+    <t>DrinkShopController, Line 26</t>
+  </si>
+  <si>
+    <t>DrinkShopController, Line 125</t>
+  </si>
+  <si>
+    <t>"Collection.isEmpty()" should be used to test for emptiness</t>
+  </si>
+  <si>
+    <t>!service.getAllProducts().stream().filter(p-&gt;p.getId()==r.getId()).toList().isEmpty()</t>
+  </si>
+  <si>
+    <t>service.getAllProducts().stream().filter(p-&gt;p.getId()==r.getId()).toList().size()&gt;0</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository, Line 12</t>
+  </si>
+  <si>
+    <t>Constructors of an "abstract" class should not be declared "public"</t>
+  </si>
+  <si>
+    <t>public FileAbstractRepository(String fileName) {}</t>
+  </si>
+  <si>
+    <t>protected FileAbstractRepository(String fileName) {}</t>
+  </si>
+  <si>
+    <t>ProductService, Line 31</t>
+  </si>
+  <si>
+    <t>ProductTest</t>
+  </si>
+  <si>
+    <t>Tests should include assertions</t>
+  </si>
+  <si>
+    <t>Add assertEquals</t>
+  </si>
+  <si>
+    <t>Effort to perform tool-based code analysis (hours): 30 min</t>
   </si>
 </sst>
 </file>
@@ -444,11 +534,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -462,16 +565,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -480,13 +577,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,19 +902,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -838,7 +928,7 @@
         <v>19</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" s="17">
         <v>233</v>
@@ -848,15 +938,15 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>234</v>
@@ -866,10 +956,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="27"/>
+      <c r="D5" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -895,13 +985,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -910,13 +1000,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -925,13 +1015,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1057,7 +1147,7 @@
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1095,19 +1185,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1120,8 +1210,8 @@
       <c r="H3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="37" t="s">
-        <v>32</v>
+      <c r="I3" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="J3" s="17">
         <v>233</v>
@@ -1131,15 +1221,15 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>234</v>
@@ -1149,10 +1239,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -1165,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -1195,11 +1285,11 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1208,11 +1298,11 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1221,11 +1311,11 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1360,7 +1450,7 @@
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1400,19 +1490,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1425,8 +1515,8 @@
       <c r="H3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="37" t="s">
-        <v>32</v>
+      <c r="I3" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="J3" s="17">
         <v>233</v>
@@ -1436,15 +1526,15 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="28"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>33</v>
+      <c r="I4" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>234</v>
@@ -1454,10 +1544,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -1470,7 +1560,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -1500,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1514,13 +1604,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1528,13 +1618,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1713,7 +1803,7 @@
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1740,10 +1830,10 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="6"/>
@@ -1754,19 +1844,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1780,7 +1870,7 @@
         <v>19</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" s="17">
         <v>233</v>
@@ -1790,13 +1880,13 @@
       <c r="C4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>33</v>
+      <c r="I4" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>234</v>
@@ -1807,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="29"/>
       <c r="H5" s="17" t="s">
@@ -1842,92 +1932,148 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
+      <c r="C13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="109.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
@@ -1936,10 +2082,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
@@ -2052,11 +2204,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
+      <c r="C32" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">
